--- a/FGScanner/Templates/SF-78-FG003_Rev.00_Stock Card.xlsx
+++ b/FGScanner/Templates/SF-78-FG003_Rev.00_Stock Card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00723\source\repos\FGScanner\FGScanner\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DABE715-9522-46DB-B4AA-86ADDAF9EA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37F7B2C-29F5-4785-BD08-F24DD9B1FB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -90,9 +90,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="166" formatCode="m/d/yyyy;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,13 +149,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="35"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -393,7 +386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -406,15 +399,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -445,47 +429,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -529,11 +495,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -917,302 +898,302 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="40" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="33" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A2" s="37"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="43"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" spans="1:6" ht="25.5">
-      <c r="A3" s="11"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="13"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:6" s="3" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="15" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1" thickBot="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="33"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="24"/>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" thickBot="1">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="37.5" customHeight="1">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A9" s="18"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
+      <c r="A9" s="39"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="22"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A11" s="18"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="22"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="22"/>
+      <c r="A12" s="39"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A13" s="18"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A14" s="18"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
+      <c r="A14" s="39"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A15" s="18"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="22"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A16" s="18"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A17" s="18"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="24"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="19"/>
     </row>
     <row r="18" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A18" s="18"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="26"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A19" s="18"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="26"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="19"/>
     </row>
     <row r="20" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A20" s="18"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="26"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A21" s="18"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="26"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A22" s="18"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="26"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A23" s="18"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="26"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A24" s="27"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="26"/>
+      <c r="A24" s="40"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="19"/>
     </row>
     <row r="25" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A25" s="30"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="29"/>
+      <c r="A25" s="41"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="20"/>
     </row>
     <row r="26" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="21"/>
     </row>
     <row r="27" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
+      <c r="A27" s="42"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="21"/>
     </row>
     <row r="28" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
+      <c r="A28" s="42"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="21"/>
     </row>
     <row r="29" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
+      <c r="A29" s="42"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="21"/>
     </row>
     <row r="30" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
+      <c r="A30" s="42"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="21"/>
     </row>
     <row r="31" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6"/>
+      <c r="A31" s="42"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="21"/>
     </row>
     <row r="32" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="6"/>
+      <c r="A32" s="42"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="21"/>
     </row>
     <row r="33" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="21"/>
     </row>
     <row r="34" spans="1:6" ht="43.15" customHeight="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="21"/>
     </row>
     <row r="35" spans="1:6" ht="30.6" customHeight="1">
       <c r="A35" s="3" t="s">
